--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.12" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.13" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.14" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.15" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -254,6 +255,13 @@
       <name val="Microsoft YaHei"/>
       <color rgb="00A8A29E"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -789,7 +797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -836,6 +844,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2007,6 +2017,964 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>7月15日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>动态拉伸5′→抢圈2×5′→转换练习3×3′→比赛4节(8′+7′+8′+8′ 节间1′) | 总约60′</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
+        <v>360</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>门将·全流程→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>360</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>门将·全流程→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>门将·全流程→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>480</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节 · 脚踝轻微不适⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>360</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="n">
+        <v>360</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节 · 仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" t="n">
+        <v>360</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="n">
+        <v>360</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节 · 左膝仍不适⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" t="n">
+        <v>360</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节 · 仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="n">
+        <v>360</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="n">
+        <v>360</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="n">
+        <v>360</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节 · 脚掌骨疼⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>360</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" t="n">
+        <v>360</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="n">
+        <v>360</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>进攻组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="n">
+        <v>420</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>防守组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>125</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>45</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>仅热身+抢圈→发烧退出🔴</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="n">
+        <v>360</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>进攻组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" t="n">
+        <v>420</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>进攻组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" t="n">
+        <v>360</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>进攻组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" t="n">
+        <v>480</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>进攻组→比赛4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" t="n">
+        <v>75</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>刘子结</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>试训·仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>试训·仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>共 28 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>未参加比赛(4人): 林楷轩、戚博、刘子结、董德 → 热身+抢圈+转换后退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>发烧退出(1人): 朱云天 → 抢圈后退出 🔴</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>试训(2人): 刘子结、董德</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>伤停(1人): 布格拉汗-斯坎旦尔(MCL)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.13" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.14" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.15" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.16" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.17" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2868,9 +2870,6 @@
           <t>缺席</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>MCL恢复期</t>
@@ -2880,7 +2879,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>刘子结</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2893,11 +2892,9 @@
           <t>部分</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>25</v>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>试训·仅热身+抢圈+转换→未参加比赛</t>
@@ -2920,11 +2917,9 @@
           <t>部分</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>25</v>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>试训·仅热身+抢圈+转换→未参加比赛</t>
@@ -2941,7 +2936,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>未参加比赛(4人): 林楷轩、戚博、刘子结、董德 → 热身+抢圈+转换后退出</t>
+          <t>未参加比赛(4人): 林楷轩、戚博、刘子洁、董德 → 热身+抢圈+转换后退出</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2950,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>试训(2人): 刘子结、董德</t>
+          <t>试训(2人): 刘子洁、董德</t>
         </is>
       </c>
     </row>
@@ -2971,6 +2966,1716 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>7月16日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>动态拉伸5′→传球练习8′→冲刺4组(5s/组)→长传球3′→战术演练20′ | 总41′</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>脚踝痛 🆕</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>205</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F7" t="n">
+        <v>205</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>246</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>41</v>
+      </c>
+      <c r="F9" t="n">
+        <v>246</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>41</v>
+      </c>
+      <c r="F10" t="n">
+        <v>246</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>246</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F12" t="n">
+        <v>246</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>41</v>
+      </c>
+      <c r="F13" t="n">
+        <v>164</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>左膝 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>41</v>
+      </c>
+      <c r="F14" t="n">
+        <v>246</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" t="n">
+        <v>205</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41</v>
+      </c>
+      <c r="F16" t="n">
+        <v>246</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" t="n">
+        <v>246</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" t="n">
+        <v>287</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>脚掌骨疼 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>41</v>
+      </c>
+      <c r="F19" t="n">
+        <v>287</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>246</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>41</v>
+      </c>
+      <c r="F21" t="n">
+        <v>205</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41</v>
+      </c>
+      <c r="F22" t="n">
+        <v>246</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="n">
+        <v>105</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>仅热身+传球+冲刺+长传→未参加战术演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>肚子不舒服·仅参加动态拉伸</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>164</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>41</v>
+      </c>
+      <c r="F26" t="n">
+        <v>287</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>41</v>
+      </c>
+      <c r="F27" t="n">
+        <v>287</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>41</v>
+      </c>
+      <c r="F28" t="n">
+        <v>164</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" t="n">
+        <v>63</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>仅热身+传球+冲刺+长传→未参加战术演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>21</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>试训·仅热身+传球+冲刺+长传→未参加战术演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>21</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>试训·仅热身+传球+冲刺+长传→未参加战术演练</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>41</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>试训跟队(待签约)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>共 29 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>部分参与(5人): 林楷轩、戚博、刘子洁、董德 → 未参加战术演练；朱云天 → 仅动态拉伸(肚子不适)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>试训(3人): 刘子洁、董德、努尔扎提-努尔兰(新加入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>伤停(1人): 布格拉汗-斯坎旦尔(MCL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>门将(3人): 张海轩脚踝痛🆕 需关注</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>7月17日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>行程日 · 全队赴大连（7/19 客场 vs 大连英博B）</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>无训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>脚踝痛·第2天 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>左膝持续 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已签约·正式入队🆕（未填晨间）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>腘绳肌微紧 🆕</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>脚掌不适持续+睡眠4 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>内踝不适 🆕</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>睡眠4·偏差</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>睡眠未填</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>已签约·正式入队🆕（未填晨间）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>左大腿后群有点紧 🆕</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>睡眠4·偏差</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>随队赴大连</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>已签约·正式入队🆕</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>共 29 人（正式名单 · 7/17 刘子洁/董德/努尔扎提-努尔兰 三人签约转正🆕）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>行程日无训练，sRPE=0；晨间问卷 26 人已填（刘子洁/董德/布格拉汗未填）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>⚠️晨间信号: 何麟立腘绳肌微紧🆕 谢锦政内踝🆕 艾沙江左大腿后群紧🆕 张海轩脚踝(第2天) 王捷左膝 巫林峰脚掌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6892,7 +8597,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>刘子结</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7878,7 +9583,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>刘子结</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -8346,14 +10051,14 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>进攻组(10人): 陈祥煜、戚博、林楷轩、朱云天、栾昊、刘子结、艾沙江、阿西江、帕尔曼江 | 防守组(14人): 张俊哲、杨文杰、王捷、谢锦政、杨翼璇、巫林峰、李金羽、张天龙、王皓文、张辉、何麟立、丁云峰、陈少豪 + 扎提</t>
+          <t>进攻组(10人): 陈祥煜、戚博、林楷轩、朱云天、栾昊、刘子洁、艾沙江、阿西江、帕尔曼江 | 防守组(14人): 张俊哲、杨文杰、王捷、谢锦政、杨翼璇、巫林峰、李金羽、张天龙、王皓文、张辉、何麟立、丁云峰、陈少豪 + 扎提</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>未参赛比赛(4人): 戚博、林楷轩、朱云天、刘子结 → 旁边抢圈 | 凌中阳/丁云峰跟队但仍停赛 | 刘子结/董德/扎提试训球员</t>
+          <t>未参赛比赛(4人): 戚博、林楷轩、朱云天、刘子洁 → 旁边抢圈 | 凌中阳/丁云峰跟队但仍停赛 | 刘子洁/董德/扎提试训球员</t>
         </is>
       </c>
     </row>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -9171,6 +9171,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -10048,17 +10049,18 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>进攻组(10人): 陈祥煜、戚博、林楷轩、朱云天、栾昊、刘子洁、艾沙江、阿西江、帕尔曼江 | 防守组(14人): 张俊哲、杨文杰、王捷、谢锦政、杨翼璇、巫林峰、李金羽、张天龙、王皓文、张辉、何麟立、丁云峰、陈少豪 + 扎提</t>
+          <t>进攻组(10人): 陈祥煜、戚博、林楷轩、朱云天、栾昊、刘子洁、艾沙江、阿西江、帕尔曼江 | 防守组(14人): 张俊哲、杨文杰、王捷、谢锦政、杨翼璇、巫林峰、李金羽、张天龙、王皓文、张辉、何麟立、丁云峰、陈少豪 + 努尔扎提-努尔兰</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>未参赛比赛(4人): 戚博、林楷轩、朱云天、刘子洁 → 旁边抢圈 | 凌中阳/丁云峰跟队但仍停赛 | 刘子洁/董德/扎提试训球员</t>
+          <t>未参赛比赛(4人): 戚博、林楷轩、朱云天、刘子洁 → 旁边抢圈 | 凌中阳/丁云峰跟队但仍停赛 | 刘子洁/董德/努尔扎提-努尔兰试训球员</t>
         </is>
       </c>
     </row>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -9171,7 +9171,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -10049,7 +10048,6 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3979,6 +3979,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -4298,7 +4299,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4497,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -4654,6 +4655,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -4664,7 +4666,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>行程日无训练，sRPE=0；晨间问卷 26 人已填（刘子洁/董德/布格拉汗未填）</t>
+          <t>行程日无训练，sRPE=0；晨间问卷 28 人已填（仅布格拉汗未填）</t>
         </is>
       </c>
     </row>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.15" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.16" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.17" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.18" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3979,7 +3980,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -4655,7 +4655,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -4674,6 +4673,942 @@
       <c r="A37" t="inlineStr">
         <is>
           <t>⚠️晨间信号: 何麟立腘绳肌微紧🆕 谢锦政内踝🆕 艾沙江左大腿后群紧🆕 张海轩脚踝(第2天) 王捷左膝 巫林峰脚掌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>7月18日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>深度牵拉12′→2-3人全场慢跑3′→中圈动态拉伸5′→抢圈5′×2→启动反应冲刺6趟→长传3′→9v9+2GK半场12′(6′×2)→传中射门7′ | 总55′</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MD-1 · 客场备战大连英博B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>脚踝痛·第4天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>110</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>330</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>220</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>220</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>275</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>220</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>275</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>330</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>220</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>220</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>脚掌骨疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>220</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" t="n">
+        <v>220</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>还有点疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>165</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" t="n">
+        <v>220</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>165</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55</v>
+      </c>
+      <c r="F28" t="n">
+        <v>165</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>55</v>
+      </c>
+      <c r="F29" t="n">
+        <v>165</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>左后群轻微紧点</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>55</v>
+      </c>
+      <c r="F30" t="n">
+        <v>165</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>165</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>太原基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>55</v>
+      </c>
+      <c r="F33" t="n">
+        <v>110</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>共 29 人 | 参训22人(全) | 缺席7人(布格拉汗MCL+太原基地4人+凌中阳/丁云峰未跟队)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MD-1轻量激活 | 均RPE 3.6 | 总sRPE 4400 | 训练强度🟢低</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>赛前: 张海轩脚踝D4 王捷左膝 巫林峰脚掌 谢锦政内踝 艾沙江左后群 | 何麟立腘绳肌已恢复</t>
         </is>
       </c>
     </row>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="12" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.16" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.17" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.18" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.19" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.20" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5617,6 +5619,1639 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>7月19日 比赛日记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>⚽ 中乙第13轮 客 vs 大连英博B 2-1 胜 | 总95′(90+5补时)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2-1 胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" t="n">
+        <v>760</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>脚踝仍痛但扛满全场✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>第69分钟登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>90+5′登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>75</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>69</v>
+      </c>
+      <c r="F18" t="n">
+        <v>483</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>第26分钟被换下</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>483</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>第26分钟被换下</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>第69分钟登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>替补未上场</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>比赛日疲劳(热身+替补席)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>85</v>
+      </c>
+      <c r="F28" t="n">
+        <v>765</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>第10分钟被换下</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F29" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26</v>
+      </c>
+      <c r="F31" t="n">
+        <v>208</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>第69分钟登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上场</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F33" t="n">
+        <v>182</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>第69分钟登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>共29人 | 首发11人+替补5人登场=16人上场 | 替补未上场6人 | 缺席7人</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>⚽ 2-1客场胜大连英博B | 总sRPE≈9344 | 均RPE5.9 | 4人RPE=10(张俊哲/张辉/艾沙江/帕尔曼江) | 赛前晨间19人填(睡9.0→原始数据需确认)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>张海轩脚踝扛住了✅ 巫林峰69′脚掌OK✅ 艾沙江左后群稍微紧⚠️ 凌中阳/丁云峰停赛结束下场可出战</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>7月20日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>行程日 · 全队从大连返回太原</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>无训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>共29人 | 行程日 全队返回太原 | 7/21放假 7/22上午太原力量房训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>晨间问卷暂未填 · 7/21恢复日后再统一收集</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10460" tabRatio="600" firstSheet="0" activeTab="16" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.18" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.19" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.20" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.22" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.23" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="36">
+  <fonts count="41">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -268,8 +270,33 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -474,8 +501,13 @@
         <bgColor rgb="001C1917"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00992828"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -654,6 +686,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -802,7 +848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -851,6 +897,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6494,7 +6553,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -7252,6 +7310,2337 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>7月22日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>上午力量房60min·12站U-L交替 + 下午场地训练70min | MD-4 · 备战7/26主场vs海门 | 一日双训·维持日</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>脚踝D9·力量房全跟·踝泵+冰敷 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>新人·轻量适应·技术动作学习 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>降量50%·RPE=6偏高·注意恢复 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>停赛休足·状态好 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>降量50%·正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>左膝髌腱·康复组·静蹲+单腿慢降·冰敷 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>降量50%·疲4→今日3·恢复中 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>⚠️睡5·降量·注意疲劳管理 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>布格拉汗</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>MCL归队D2·上肢正常·下肢自重+MCL保护·冰敷</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>脚掌史·康复组·坐姿优先·冰敷 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>🆕脚腕疼·降量50%·关注新信号 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>内踝已恢复·正常组·训练OK | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>正常 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>新人·训练投入高 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>新人·轻量适应 | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>新人·RPE待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>降量50% | 下午场地OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>艾沙江</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>后群观察·臀桥代深蹲·不硬拉·不北欧</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>降量50%·睡4·三高已改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>降量50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>努尔扎提</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>下午场地训练 · 70min · MD-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>动态拉伸 5min</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>抢圈 Rondo 5min×2组</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>传接球 Passing 2min×3组</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>射门专项 Shooting 15min（①②两套线路人员交换）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 中场斜插远射线路</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 肋部渗透 + 门前终结线路</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>分队对抗 Match 15min · 13v13+4门将 · 间歇1min</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>共31人 | AM力量房(均RPE~4.5)+PM场地70min(均RPE~4.5) | 一日双训·维持日·总sRPE~16600</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>🆕信号: 张辉脚腕疼 | ⚠️何麟立睡5 | 布格拉汗归队D2全天OK | 王捷/巫林峰/张海轩按康复方案 | 场地训练13v13含4门将·强度适中</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>7月23日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>MD-3 · 三球门11v11对抗+头球游戏+4v4体能 · 备战7/26主场vs南通海门珂缔缘</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>全队50min：动态激活5′→头球游戏9′(手抛4′+脚发5′)→11v11自由人×2组(6′×2)→11v11三球门正式20′ | 同步4v4体能(刘子洁/吕佳骏/董德/朱云天/林楷轩/布格拉汗) | 间歇1′30″</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>脚踝D10·RPE偏高·需关注</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>肩膀疼·正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>新人·正常适应</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>⚠️⚠️⚠️ RPE=8全队最高·7/19跑10km+7/22力量全量→累积疲劳·D-3必须降量</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>RPE偏高·停赛休足但今日反应强·三球门覆盖大</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ RPE=7·连续两天偏高·睡3疲3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>⚠️左膝酸痛=4·RPE=7·需评估髌腱负荷</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>正常酸痛·RPE偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>正常酸痛·RPE偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>4v4前10min后换回主组</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>4v4组·体能教练带·投入正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>睡质从5→2·恢复良好</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>MCL D+2·4v4参与·变向可控✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>脚掌史·正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>⚠️肌肉酸·7/19跑10km+脚腕疼史·需监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>RPE偏高·内踝已恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>4v4组·肌肉酸痛=4·正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>200</v>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>4v4组·正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>4v4组·睡4·RPE低·投入度待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>4v4</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>4v4组·10min替换杨文杰·新人适应</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>新人·RPE待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>恢复良好·RPE回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>后群观察中·正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>睡眠4→3改善·RPE稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>未填数据·待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>下午场地训练 · 70min · MD-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>共32人 · MD-3 · 均RPE≈5.5 · 11v11三球门+头球游戏+4v4 · 张俊哲RPE=8⚠️ · 备战7/26主场</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>抢圈 Rondo 5min×2组</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>传接球 Passing 2min×3组</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>射门专项 Shooting 15min（①②两套线路人员交换）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 中场斜插远射线路</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 肋部渗透 + 门前终结线路</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>分队对抗 Match 15min · 13v13+4门将 · 间歇1min</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>共31人 | AM力量房(均RPE~4.5)+PM场地70min(均RPE~4.5) | 一日双训·维持日·总sRPE~16600</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>🆕信号: 张辉脚腕疼 | ⚠️何麟立睡5 | 布格拉汗归队D2全天OK | 王捷/巫林峰/张海轩按康复方案 | 场地训练13v13含4门将·强度适中</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -8497,7 +8497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>离队</t>
         </is>
       </c>
       <c r="D35" s="23" t="n"/>
@@ -9516,7 +9516,7 @@
       <c r="F35" s="24" t="n"/>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>未填数据·待补</t>
+          <t>租借→海门珂缔缘</t>
         </is>
       </c>
     </row>
@@ -9621,9 +9621,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A44:G44"/>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="20" activeTab="32" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="20" activeTab="33" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.7" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26378,6 +26379,921 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>8月11日 训练课记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D+2恢复 · 慢跑12'→拉伸热身8'→颠球游戏→井字棋游戏→头球游戏→慢跑10' · 总60'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t>时长min</t>
+        </is>
+      </c>
+      <c r="F4" s="42" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>左腿后群有点反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>内收肌紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>180</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="n">
+        <v>180</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>小腿酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" t="n">
+        <v>180</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="n">
+        <v>180</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>脚腕微痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="n">
+        <v>180</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>120</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" t="n">
+        <v>180</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="n">
+        <v>120</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="n">
+        <v>120</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" t="n">
+        <v>120</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" t="n">
+        <v>180</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>左膝盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="n">
+        <v>120</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" t="n">
+        <v>180</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" t="n">
+        <v>180</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" t="n">
+        <v>300</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" t="n">
+        <v>180</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" t="n">
+        <v>120</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" t="n">
+        <v>120</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>脚趾头肿</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8/11 D+2 · 27人参训·总sRPE=4140 · 均RPE≈2.6 · 艾沙江RPE=5偏高⚠️</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="20" activeTab="33" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="20" activeTab="34" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26479,7 +26480,6 @@
       <c r="F5" t="n">
         <v>180</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>左腿后群有点反应</t>
@@ -26511,7 +26511,6 @@
       <c r="F6" t="n">
         <v>120</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>内收肌紧</t>
@@ -26543,7 +26542,6 @@
       <c r="F7" t="n">
         <v>120</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26570,7 +26568,6 @@
       <c r="F8" t="n">
         <v>180</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26597,7 +26594,6 @@
       <c r="F9" t="n">
         <v>180</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26624,7 +26620,6 @@
       <c r="F10" t="n">
         <v>120</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26651,7 +26646,6 @@
       <c r="F11" t="n">
         <v>120</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26678,7 +26672,6 @@
       <c r="F12" t="n">
         <v>120</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26705,7 +26698,6 @@
       <c r="F13" t="n">
         <v>180</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>小腿酸痛</t>
@@ -26737,7 +26729,6 @@
       <c r="F14" t="n">
         <v>180</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>紧</t>
@@ -26769,7 +26760,6 @@
       <c r="F15" t="n">
         <v>120</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26796,7 +26786,6 @@
       <c r="F16" t="n">
         <v>180</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>脚踝痛</t>
@@ -26828,7 +26817,6 @@
       <c r="F17" t="n">
         <v>120</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>脚腕微痛</t>
@@ -26860,7 +26848,6 @@
       <c r="F18" t="n">
         <v>180</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26887,7 +26874,6 @@
       <c r="F19" t="n">
         <v>120</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>腰疼</t>
@@ -26919,7 +26905,6 @@
       <c r="F20" t="n">
         <v>180</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -26946,7 +26931,6 @@
       <c r="F21" t="n">
         <v>120</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26973,7 +26957,6 @@
       <c r="F22" t="n">
         <v>120</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -27000,7 +26983,6 @@
       <c r="F23" t="n">
         <v>120</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -27027,7 +27009,6 @@
       <c r="F24" t="n">
         <v>180</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>左膝盖</t>
@@ -27059,7 +27040,6 @@
       <c r="F25" t="n">
         <v>120</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -27086,7 +27066,6 @@
       <c r="F26" t="n">
         <v>180</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -27113,7 +27092,6 @@
       <c r="F27" t="n">
         <v>180</v>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -27140,7 +27118,6 @@
       <c r="F28" t="n">
         <v>300</v>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -27167,7 +27144,6 @@
       <c r="F29" t="n">
         <v>180</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -27194,7 +27170,6 @@
       <c r="F30" t="n">
         <v>120</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -27221,7 +27196,6 @@
       <c r="F31" t="n">
         <v>120</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -27239,7 +27213,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>脚趾头肿</t>
@@ -27262,7 +27235,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -27280,7 +27252,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -27288,6 +27259,899 @@
           <t>8/11 D+2 · 27人参训·总sRPE=4140 · 均RPE≈2.6 · 艾沙江RPE=5偏高⚠️</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>训练结构</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>热身5min + 抢圈7min + 头球练习6min + 战术演练15min + 半场定位球10min（含休息约50min）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>总时长(min)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>250</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>睡眠4酸痛3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>250</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>内收肌紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>200</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>150</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>脚趾恢复中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="n">
+        <v>250</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" t="n">
+        <v>150</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="n">
+        <v>300</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" t="n">
+        <v>150</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" t="n">
+        <v>250</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>50</v>
+      </c>
+      <c r="F33" t="n">
+        <v>200</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" t="n">
+        <v>200</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="n">
+        <v>200</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -27370,7 +27370,6 @@
       <c r="F6" t="n">
         <v>100</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27397,7 +27396,6 @@
       <c r="F7" t="n">
         <v>150</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27424,7 +27422,6 @@
       <c r="F8" t="n">
         <v>150</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27451,7 +27448,6 @@
       <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27478,7 +27474,6 @@
       <c r="F10" t="n">
         <v>150</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27505,7 +27500,6 @@
       <c r="F11" t="n">
         <v>200</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27532,7 +27526,6 @@
       <c r="F12" t="n">
         <v>200</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27559,7 +27552,6 @@
       <c r="F13" t="n">
         <v>150</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27586,7 +27578,6 @@
       <c r="F14" t="n">
         <v>150</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27644,7 +27635,6 @@
       <c r="F16" t="n">
         <v>250</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27702,7 +27692,11 @@
       <c r="F18" t="n">
         <v>150</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27717,13 +27711,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -27781,7 +27785,6 @@
       <c r="F21" t="n">
         <v>200</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -27808,7 +27811,6 @@
       <c r="F22" t="n">
         <v>150</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -27835,7 +27837,6 @@
       <c r="F23" t="n">
         <v>300</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -27853,9 +27854,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>脚趾恢复中</t>
@@ -27887,7 +27885,6 @@
       <c r="F25" t="n">
         <v>250</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -27914,7 +27911,6 @@
       <c r="F26" t="n">
         <v>150</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -27941,7 +27937,11 @@
       <c r="F27" t="n">
         <v>100</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -27968,7 +27968,11 @@
       <c r="F28" t="n">
         <v>300</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -27986,10 +27990,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28008,13 +28008,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -28043,7 +28043,6 @@
       <c r="F31" t="n">
         <v>150</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -28070,7 +28069,6 @@
       <c r="F32" t="n">
         <v>250</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -28097,7 +28095,6 @@
       <c r="F33" t="n">
         <v>200</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -28124,7 +28121,6 @@
       <c r="F34" t="n">
         <v>200</v>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -28151,7 +28147,6 @@
       <c r="F35" t="n">
         <v>200</v>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19700" windowHeight="9840" tabRatio="600" firstSheet="26" activeTab="36" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19700" windowHeight="9840" tabRatio="600" firstSheet="11" activeTab="37" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.6" sheetId="1" state="visible" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.14" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.15" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5979,7 +5980,8 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="6"/>
+    <col width="12.4134615384615" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
@@ -7525,7 +7527,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="47.9038461538462" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -7561,7 +7563,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>球员RPE</t>
+          <t>RPE(0-10)</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
@@ -7602,12 +7604,14 @@
         </is>
       </c>
       <c r="D5" s="20" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>840</v>
+      </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>脚踝D9·力量房全跟·踝泵+冰敷 | 下午场地OK</t>
@@ -7631,12 +7635,14 @@
         </is>
       </c>
       <c r="D6" s="20" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>770</v>
+      </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7660,12 +7666,14 @@
         </is>
       </c>
       <c r="D7" s="20" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>770</v>
+      </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7689,12 +7697,14 @@
         </is>
       </c>
       <c r="D8" s="20" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>500</v>
+      </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
           <t>新人·轻量适应·技术动作学习 | 下午场地OK</t>
@@ -7718,12 +7728,14 @@
         </is>
       </c>
       <c r="D9" s="20" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>780</v>
+      </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
           <t>降量50%·RPE=6偏高·注意恢复 | 下午场地OK</t>
@@ -7747,12 +7759,14 @@
         </is>
       </c>
       <c r="D10" s="20" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>710</v>
+      </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7776,12 +7790,14 @@
         </is>
       </c>
       <c r="D11" s="20" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>770</v>
+      </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
           <t>停赛休足·状态好 | 下午场地OK</t>
@@ -7805,12 +7821,14 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7834,12 +7852,14 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>770</v>
+      </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
           <t>降量50%·正常 | 下午场地OK</t>
@@ -7863,12 +7883,14 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>710</v>
+      </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
           <t>左膝髌腱·康复组·静蹲+单腿慢降·冰敷 | 下午场地OK</t>
@@ -7892,12 +7914,14 @@
         </is>
       </c>
       <c r="D15" s="20" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>770</v>
+      </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
           <t>降量50%·疲4→今日3·恢复中 | 下午场地OK</t>
@@ -7921,12 +7945,14 @@
         </is>
       </c>
       <c r="D16" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7950,12 +7976,14 @@
         </is>
       </c>
       <c r="D17" s="20" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>710</v>
+      </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -7979,12 +8007,14 @@
         </is>
       </c>
       <c r="D18" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -8008,12 +8038,14 @@
         </is>
       </c>
       <c r="D19" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
           <t>⚠️睡5·降量·注意疲劳管理 | 下午场地OK</t>
@@ -8037,12 +8069,14 @@
         </is>
       </c>
       <c r="D20" s="20" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F20" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>570</v>
+      </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
           <t>MCL归队D2·上肢正常·下肢自重+MCL保护·冰敷</t>
@@ -8066,12 +8100,14 @@
         </is>
       </c>
       <c r="D21" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F21" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
           <t>脚掌史·康复组·坐姿优先·冰敷 | 下午场地OK</t>
@@ -8095,12 +8131,14 @@
         </is>
       </c>
       <c r="D22" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F22" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
           <t>🆕脚腕疼·降量50%·关注新信号 | 下午场地OK</t>
@@ -8124,12 +8162,14 @@
         </is>
       </c>
       <c r="D23" s="20" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F23" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>640</v>
+      </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
           <t>内踝已恢复·正常组·训练OK | 下午场地OK</t>
@@ -8153,12 +8193,14 @@
         </is>
       </c>
       <c r="D24" s="20" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F24" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>640</v>
+      </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -8182,12 +8224,14 @@
         </is>
       </c>
       <c r="D25" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -8211,12 +8255,14 @@
         </is>
       </c>
       <c r="D26" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F26" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -8240,12 +8286,14 @@
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F27" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
           <t>正常 | 下午场地OK</t>
@@ -8269,12 +8317,14 @@
         </is>
       </c>
       <c r="D28" s="20" t="n">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F28" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>780</v>
+      </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
           <t>新人·训练投入高 | 下午场地OK</t>
@@ -8298,12 +8348,14 @@
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>510</v>
+      </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
           <t>新人·轻量适应 | 下午场地OK</t>
@@ -8358,12 +8410,14 @@
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>640</v>
+      </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
           <t>降量50% | 下午场地OK</t>
@@ -8387,12 +8441,14 @@
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>710</v>
+      </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
           <t>后群观察·臀桥代深蹲·不硬拉·不北欧</t>
@@ -8416,12 +8472,14 @@
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>840</v>
+      </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
           <t>降量50%·睡4·三高已改善</t>
@@ -8445,12 +8503,14 @@
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F34" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>640</v>
+      </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
           <t>降量50%</t>
@@ -8474,12 +8534,14 @@
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F35" s="21" t="n"/>
+        <v>130</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>700</v>
+      </c>
       <c r="G35" s="20" t="inlineStr">
         <is>
           <t>正常</t>
@@ -28010,7 +28072,6 @@
       <c r="F30" t="n">
         <v>250</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -28255,7 +28316,6 @@
       <c r="F6" t="n">
         <v>150</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28282,7 +28342,6 @@
       <c r="F7" t="n">
         <v>150</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28309,7 +28368,6 @@
       <c r="F8" t="n">
         <v>150</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28336,7 +28394,6 @@
       <c r="F9" t="n">
         <v>150</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28363,7 +28420,6 @@
       <c r="F10" t="n">
         <v>150</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28390,7 +28446,6 @@
       <c r="F11" t="n">
         <v>150</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28448,7 +28503,6 @@
       <c r="F13" t="n">
         <v>150</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28506,7 +28560,6 @@
       <c r="F15" t="n">
         <v>150</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28533,7 +28586,6 @@
       <c r="F16" t="n">
         <v>150</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28591,7 +28643,6 @@
       <c r="F18" t="n">
         <v>100</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28618,7 +28669,6 @@
       <c r="F19" t="n">
         <v>150</v>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -28645,7 +28695,6 @@
       <c r="F20" t="n">
         <v>150</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -28672,7 +28721,6 @@
       <c r="F21" t="n">
         <v>150</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -28792,7 +28840,6 @@
       <c r="F25" t="n">
         <v>150</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -28881,7 +28928,6 @@
       <c r="F28" t="n">
         <v>150</v>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -28908,7 +28954,6 @@
       <c r="F29" t="n">
         <v>150</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28935,7 +28980,6 @@
       <c r="F30" t="n">
         <v>150</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -28962,7 +29006,6 @@
       <c r="F31" t="n">
         <v>150</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -28989,7 +29032,6 @@
       <c r="F32" t="n">
         <v>150</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -29016,7 +29058,6 @@
       <c r="F33" t="n">
         <v>150</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -29060,10 +29101,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29077,76 +29114,930 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="14.4134615384615" customWidth="1" min="4" max="4"/>
+    <col width="14.2596153846154" customWidth="1" min="5" max="5"/>
+    <col width="15.2211538461538" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>训练结构</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>热身5min+抢圈6min×2组+冲刺4次(2min)+两人传球3min+战术演练15min+传中射门(50min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>总时长(min)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>略不舒服</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>黄牌停赛·未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>8月15日 比赛日记录</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>训练结构</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>热身5min+抢圈6min×2组+冲刺4次(2min)+两人传球3min+战术演练15min+传中射门(50min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>总时长(min)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>50</v>
+          <t>⚽ 中乙第21轮 · 客场 vs 青岛红狮 · 0-1 负 · 5-3-2 · 90min · 曹睿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>参与</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>球员RPE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>时长min</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>教练技评</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>球员</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>位置</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>参与</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RPE(0-10)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>时长(min)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>sRPE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>教练技评</t>
+          <t>首发11人 (5-3-2)</t>
         </is>
       </c>
     </row>
@@ -29163,86 +30054,90 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>250</v>
+        <v>720</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>脚踝痛</t>
+          <t>首发全场·脚踝</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杨卓燠</t>
+          <t>张俊哲</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>腰疼</t>
+          <t>首发全场·RPE=10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>王款(U21)</t>
+          <t>张天龙</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>720</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>张俊哲</t>
+          <t>凌中阳</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -29252,28 +30147,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>300</v>
+        <v>441</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>略不舒服</t>
+          <t>首发63'↓</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>张天龙</t>
+          <t>王皓文(U21)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -29283,24 +30178,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>720</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>凌中阳</t>
+          <t>丁云峰</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -29310,190 +30209,190 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>720</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陈少豪</t>
+          <t>何麟立</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>711</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>首发79'↓</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>李金羽</t>
+          <t>巫林峰</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>250</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>首发56'↓</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>王捷(U21)</t>
+          <t>陈祥煜</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>200</v>
+        <v>810</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>左膝</t>
+          <t>首发全场</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>王皓文(U21)</t>
+          <t>艾沙江-库尔班</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>250</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>810</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>首发全场·队长</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>丁云峰</t>
+          <t>帕尔曼江-克尤木</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>200</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>900</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>首发全场·RPE=10</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>杨文杰</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" t="n">
-        <v>200</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>替补登场</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>何麟立</t>
+          <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -29503,419 +30402,427 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>63'↑·MCL首秀</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>布格拉汗-斯坎旦尔</t>
+          <t>阿西江-白山</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>56'↑</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>巫林峰</t>
+          <t>努尔扎提-努尔兰</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>200</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>79'↑</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>栾昊(U21)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>50</v>
-      </c>
-      <c r="F21" t="n">
-        <v>150</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>杨翼璇</t>
+          <t>杨卓燠</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>吕佳骏</t>
+          <t>王款(U21)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>陈祥煜</t>
+          <t>陈少豪</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>200</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>艾沙江-库尔班</t>
+          <t>李金羽</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>250</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>帕尔曼江-克尤木</t>
+          <t>王捷(U21)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>250</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>阿西江-白山</t>
+          <t>杨文杰</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>200</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>努尔扎提-努尔兰</t>
+          <t>栾昊(U21)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>250</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>王熙博</t>
+          <t>杨翼璇</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未随队</t>
+          <t>替补未登场</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>刘子洁</t>
+          <t>吕佳骏</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未随队</t>
+          <t>替补未登场</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>张辉</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>黄牌停赛·未跟队</t>
+          <t>未随队/未跟队</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>谢锦政</t>
+          <t>王熙博</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未跟队</t>
+          <t>未随队</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>林楷轩(U21)</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未跟队</t>
+          <t>未随队</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>朱云天(U21)</t>
+          <t>张辉</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -29925,40 +30832,107 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未跟队</t>
+          <t>黄牌停赛·未跟队</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>董德</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8/15 ⚽客0-1青岛红狮 · 14人上场·总sRPE=8760 · 5-3-2 · 曹睿</t>
         </is>
       </c>
     </row>

--- a/public/share/data/训练课记录.xlsx
+++ b/public/share/data/训练课记录.xlsx
@@ -28254,6 +28254,7 @@
         <v>50</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -28807,7 +28808,7 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
